--- a/images_src/ReL4系统调用.xlsx
+++ b/images_src/ReL4系统调用.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LynxPeng\projects\GraduationProjectRecords\paper\images_src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5B8E05-A4E5-4D1E-BC70-BA6FDDEA689A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2FE9F9-0437-4930-98B8-EB3A8C83D005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{0CED8242-9685-446E-BABB-9247362C6CB9}"/>
+    <workbookView xWindow="7097" yWindow="549" windowWidth="10123" windowHeight="6728" activeTab="1" xr2:uid="{0CED8242-9685-446E-BABB-9247362C6CB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>同步</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,19 +51,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TAIC单核</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TAIC多核</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>单核陷入频率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>多核陷入频率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>seL4同步</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReL4异步单核</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReL4异步多核</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReL4TAIC单核</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ReL4TAIC多核</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -739,7 +751,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>同步</c:v>
+                  <c:v>seL4同步</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -823,7 +835,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>异步单核</c:v>
+                  <c:v>ReL4异步单核</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -907,7 +919,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>异步多核</c:v>
+                  <c:v>ReL4异步多核</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -991,7 +1003,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TAIC单核</c:v>
+                  <c:v>ReL4TAIC单核</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1075,7 +1087,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TAIC多核</c:v>
+                  <c:v>ReL4TAIC多核</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1433,7 +1445,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1470,7 +1482,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -1532,7 +1544,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1569,7 +1581,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -1689,6 +1701,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1372188848"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -1869,7 +1882,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>同步</c:v>
+                  <c:v>seL4同步</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1947,7 +1960,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>异步单核</c:v>
+                  <c:v>ReL4异步单核</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2025,7 +2038,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>异步多核</c:v>
+                  <c:v>ReL4异步多核</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2103,7 +2116,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TAIC单核</c:v>
+                  <c:v>ReL4TAIC单核</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2181,7 +2194,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TAIC多核</c:v>
+                  <c:v>ReL4TAIC多核</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2575,6 +2588,831 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="zh-CN" b="0"/>
+              <a:t>不同并发度下单次系统调用所耗时钟周期</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+              <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="7.4242499134990855E-2"/>
+          <c:y val="0.15516492855340985"/>
+          <c:w val="0.89315967267564556"/>
+          <c:h val="0.75621994393575565"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>seL4同步</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="AADCDE"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet2!$B$5:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$5:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>9960</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9960</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9960</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9960</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9960</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9960</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5E57-494D-AB0D-28F1997596B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ReL4异步单核</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="386694"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet2!$B$5:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$D$5:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>22000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8250</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7510</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5E57-494D-AB0D-28F1997596B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ReL4异步多核</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="72BDD7"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet2!$B$5:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$E$5:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>18250</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7250</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7200</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5E57-494D-AB0D-28F1997596B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$F$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ReL4TAIC单核</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FED070"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet2!$B$5:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$F$5:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>11000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7450</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7450</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5E57-494D-AB0D-28F1997596B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$G$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ReL4TAIC多核</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="E86059"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet2!$B$5:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$G$5:$G$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>7450</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-5E57-494D-AB0D-28F1997596B9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:axId val="1549358064"/>
+        <c:axId val="1549362864"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1549358064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                    <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-CN" altLang="en-US"/>
+                  <a:t>并发度</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                  <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-CN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1549362864"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1549362864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="23000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                    <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="zh-CN" altLang="en-US"/>
+                  <a:t>时钟周期（个）</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.1354418179943388E-2"/>
+              <c:y val="7.3528482322778255E-2"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                  <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-CN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="in"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="11263F"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1549358064"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="tr"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.86658652297147887"/>
+          <c:y val="9.2934926595867079E-2"/>
+          <c:w val="0.12199434918014558"/>
+          <c:h val="0.25347161455589645"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+              <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr b="0">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+          <a:latin typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+          <a:ea typeface="黑体" panose="02010609060101010101" pitchFamily="49" charset="-122"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2695,6 +3533,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -3702,6 +4580,509 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4316,6 +5697,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>132183</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>85528</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>575388</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>108857</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="图表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D69A1124-1C20-44B8-9888-E0C8CE8E2701}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4757,25 +6176,25 @@
   <sheetData>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C4" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
         <v>3</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>4</v>
-      </c>
-      <c r="H4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
